--- a/docs/evidence/20261025_NonNV_TPU_Trainium/NonNV_TPU_Trainium.xlsx
+++ b/docs/evidence/20261025_NonNV_TPU_Trainium/NonNV_TPU_Trainium.xlsx
@@ -21664,7 +21664,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.75–0.9</t>
+      <t xml:space="preserve">0.75</t>
     </r>
     <r>
       <rPr>
@@ -21702,7 +21702,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.25</t>
+      <t xml:space="preserve">0.24</t>
     </r>
     <r>
       <rPr>
